--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_24-09-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_24-09-2025.xlsx
@@ -528,37 +528,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>£10.45</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>£10.45</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>£10.45</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>£10.50</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>£10.50</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>£10.50</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>£10.50</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.82</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -576,25 +576,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -639,17 +639,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.30</t>
+          <t>£11.99</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.30</t>
+          <t>£11.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.30</t>
+          <t>£11.99</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -687,25 +687,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -750,17 +750,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.35</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.35</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£16.05</t>
+          <t>£15.88</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -798,25 +798,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -861,17 +861,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£15.60</t>
+          <t>£15.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.60</t>
+          <t>£15.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£15.60</t>
+          <t>£15.45</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£17.58</t>
+          <t>£17.15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -909,25 +909,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -972,17 +972,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£20.25</t>
+          <t>£19.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£20.25</t>
+          <t>£19.80</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£20.25</t>
+          <t>£19.80</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£21.68</t>
+          <t>£21.29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1020,25 +1020,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£22.50</t>
+          <t>£21.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£22.50</t>
+          <t>£21.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£22.50</t>
+          <t>£21.75</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£23.68</t>
+          <t>£23.23</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1131,25 +1131,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1194,17 +1194,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£22.02</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£22.02</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£22.02</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£23.00</t>
+          <t>£23.53</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1242,25 +1242,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1305,17 +1305,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£26.22</t>
+          <t>£27.40</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1353,25 +1353,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>£27.30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>£27.30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>£27.30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1464,25 +1464,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.88</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.88</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.88</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£29.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1575,25 +1575,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£36.35</t>
+          <t>£35.83</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1686,25 +1686,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1749,17 +1749,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£32.95</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£32.95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£32.95</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£35.00</t>
+          <t>£36.15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1797,25 +1797,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1860,17 +1860,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£41.15</t>
+          <t>£43.33</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1908,25 +1908,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1971,17 +1971,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£41.50</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£41.50</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£41.50</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£42.00</t>
+          <t>£45.83</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2019,25 +2019,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2082,37 +2082,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>£40.92</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>£40.92</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>£40.92</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>£40.95</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>£40.95</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>£40.95</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>£40.95</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£42.68</t>
+          <t>£45.83</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2130,25 +2130,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff769151eb5+80197]
-	GetHandleVerifier [0x0x7ff769151f10+80288]
-	(No symbol) [0x0x7ff768ed02fa]
-	(No symbol) [0x0x7ff768f27cd7]
-	(No symbol) [0x0x7ff768f27f9c]
-	(No symbol) [0x0x7ff768f7ba87]
-	(No symbol) [0x0x7ff768f503bf]
-	(No symbol) [0x0x7ff768f787fb]
-	(No symbol) [0x0x7ff768f50153]
-	(No symbol) [0x0x7ff768f18b02]
-	(No symbol) [0x0x7ff768f198d3]
-	GetHandleVerifier [0x0x7ff76940e83d+2949837]
-	GetHandleVerifier [0x0x7ff769408c6a+2926330]
-	GetHandleVerifier [0x0x7ff7694286c7+3055959]
-	GetHandleVerifier [0x0x7ff76916cfee+191102]
-	GetHandleVerifier [0x0x7ff7691750af+224063]
-	GetHandleVerifier [0x0x7ff76915af64+117236]
-	GetHandleVerifier [0x0x7ff76915b119+117673]
-	GetHandleVerifier [0x0x7ff7691410a8+11064]
+	GetHandleVerifier [0x0x7ff665481eb5+80197]
+	GetHandleVerifier [0x0x7ff665481f10+80288]
+	(No symbol) [0x0x7ff6652002fa]
+	(No symbol) [0x0x7ff665257cd7]
+	(No symbol) [0x0x7ff665257f9c]
+	(No symbol) [0x0x7ff6652aba87]
+	(No symbol) [0x0x7ff6652803bf]
+	(No symbol) [0x0x7ff6652a87fb]
+	(No symbol) [0x0x7ff665280153]
+	(No symbol) [0x0x7ff665248b02]
+	(No symbol) [0x0x7ff6652498d3]
+	GetHandleVerifier [0x0x7ff66573e83d+2949837]
+	GetHandleVerifier [0x0x7ff665738c6a+2926330]
+	GetHandleVerifier [0x0x7ff6657586c7+3055959]
+	GetHandleVerifier [0x0x7ff66549cfee+191102]
+	GetHandleVerifier [0x0x7ff6654a50af+224063]
+	GetHandleVerifier [0x0x7ff66548af64+117236]
+	GetHandleVerifier [0x0x7ff66548b119+117673]
+	GetHandleVerifier [0x0x7ff6654710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
